--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0219.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0219.xlsx
@@ -769,7 +769,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Cộng Hưởng Giả dưới cấp 50 sẽ được tăng Cấp Cộng Hưởng và Cấp Vũ Khí lên 50, ngoại trừ Cộng Hưởng Giả thử nghiệm.</t>
+          <t>Resonator dưới cấp 50 sẽ được tăng Cấp Cộng Hưởng và Cấp Vũ Khí lên 50, ngoại trừ Resonator thử nghiệm.</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Cộng Hưởng Giả dưới cấp 60 sẽ được tăng Cấp Cộng Hưởng và Cấp Vũ Khí lên 60, ngoại trừ Cộng Hưởng Giả thử nghiệm.</t>
+          <t>Resonator dưới cấp 60 sẽ được tăng Cấp Cộng Hưởng và Cấp Vũ Khí lên 60, ngoại trừ Resonator thử nghiệm.</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Cộng Hưởng Giả dưới cấp 70 sẽ được tăng Cấp Cộng Hưởng và Cấp Vũ Khí lên 70, ngoại trừ Cộng Hưởng Giả thử nghiệm.</t>
+          <t>Resonator dưới cấp 70 sẽ được tăng Cấp Cộng Hưởng và Cấp Vũ Khí lên 70, ngoại trừ Resonator thử nghiệm.</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Cộng Hưởng Giả dưới cấp 80 sẽ được tăng Cấp Cộng Hưởng và Cấp Vũ Khí lên 80, ngoại trừ Cộng Hưởng Giả thử nghiệm.</t>
+          <t>Resonator dưới cấp 80 sẽ được tăng Cấp Cộng Hưởng và Cấp Vũ Khí lên 80, ngoại trừ Resonator thử nghiệm.</t>
         </is>
       </c>
     </row>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Cộng Hưởng Giả dưới cấp 80 sẽ được tăng Cấp Cộng Hưởng và Cấp Vũ Khí lên 80, ngoại trừ Cộng Hưởng Giả thử nghiệm.</t>
+          <t>Resonator dưới cấp 80 sẽ được tăng Cấp Cộng Hưởng và Cấp Vũ Khí lên 80, ngoại trừ Resonator thử nghiệm.</t>
         </is>
       </c>
     </row>
@@ -1549,7 +1549,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>{0} Unlocked</t>
+          <t>{0} Đã mở khóa</t>
         </is>
       </c>
     </row>
@@ -2784,7 +2784,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Em nên đứng chính giữa để cúi chào cuối cùng.</t>
+          <t>Cậu nên đứng chính giữa để cúi chào cuối cùng đi.</t>
         </is>
       </c>
     </row>
@@ -5059,7 +5059,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>Hãy triển khai ít nhất 1 Cộng Hưởng Giả.</t>
+          <t>Hãy triển khai ít nhất 1 Resonator.</t>
         </is>
       </c>
     </row>
@@ -5124,7 +5124,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>Vẫn còn Cộng Hưởng Giả chưa triển khai. Cậu chắc chắn muốn bắt đầu thử thách chứ?</t>
+          <t>Vẫn còn Resonator chưa triển khai. Cậu chắc chắn muốn bắt đầu thử thách chứ?</t>
         </is>
       </c>
     </row>
@@ -5319,7 +5319,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>Không đủ Lollo Stamps. Hoàn thành Chiến Dịch Lollo để nhận thêm Lollo Stamps.</t>
+          <t>Không đủ Tem Lollo. Hoàn thành Chiến dịch Lollo để nhận thêm Tem Lollo.</t>
         </is>
       </c>
     </row>
@@ -6619,7 +6619,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>Nỗ lực của chúng ta đã thu hút sự chú ý của một người quen đấy. Đi chào hỏi nào, Rover!</t>
+          <t>Nỗ lực của chúng ta đã thu hút sự chú ý của một người quen đấy. Đi chào hỏi nào, Vận Mệnh Giả!</t>
         </is>
       </c>
     </row>
@@ -8504,7 +8504,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>Muốn cùng ta biến "khả năng" thành "hiện thực" không?</t>
+          <t>Muốn cùng tao biến "khả năng" thành "hiện thực" không?</t>
         </is>
       </c>
     </row>
@@ -8699,7 +8699,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>Những khúc ngoặt... Hừm, ta cũng quen rồi.</t>
+          <t>Những khúc ngoặt... Hừm, tao cũng quen rồi.</t>
         </is>
       </c>
     </row>
@@ -8764,7 +8764,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>Hê, ta biết mà! Đây gọi là "bước ngoặt" trong câu chuyện đấy.</t>
+          <t>Hê, tao biết mà! Đây gọi là "bước ngoặt" trong câu chuyện đấy.</t>
         </is>
       </c>
     </row>
@@ -9609,7 +9609,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>Những chuyện lớn thế này khiến ta lo lắng. Phải luôn tỉnh táo! Nếu gặp rắc rối, tìm ta hoặc một Ranger khác nhé.</t>
+          <t>Những chuyện lớn thế này khiến tao lo lắng. Phải luôn tỉnh táo! Nếu gặp rắc rối, tìm tao hoặc một Ranger khác nhé.</t>
         </is>
       </c>
     </row>
@@ -10779,7 +10779,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>Thời điểm nào để thư giãn tốt hơn lễ hội chứ? Ta biết chỗ tắm nắng ngon nhất, đi cùng không?</t>
+          <t>Thời điểm nào để thư giãn tốt hơn lễ hội chứ? Tao biết chỗ tắm nắng ngon nhất, đi cùng không?</t>
         </is>
       </c>
     </row>
@@ -12404,7 +12404,7 @@
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>Hành trình phía trước có thể đưa cậu đi xa, nhưng thành phố này và mọi người ở đây sẽ luôn chào đón cậu trở về. Chúc mừng Trung Thu, Rover!</t>
+          <t>Hành trình phía trước có thể đưa cậu đi xa, nhưng thành phố này và mọi người ở đây sẽ luôn chào đón cậu trở về. Chúc mừng Trung Thu, Vận Mệnh Giả!</t>
         </is>
       </c>
     </row>
@@ -13769,7 +13769,7 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>Lần này ta muốn phá kỷ lục cá nhân trong "Moon Shooter"!</t>
+          <t>Lần này tao muốn phá kỷ lục cá nhân trong "Moon Shooter"!</t>
         </is>
       </c>
     </row>
@@ -18254,7 +18254,7 @@
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>&lt;color=#f9fb35ff&gt;{0}&lt;/color&gt;/{1}</t>
+          <t>{0}/{1}</t>
         </is>
       </c>
     </row>
@@ -18449,7 +18449,7 @@
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t>Remaining: {0}</t>
+          <t>Còn lại: {0}</t>
         </is>
       </c>
     </row>
@@ -18644,7 +18644,7 @@
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>Nâng cấp Cộng Hưởng Giả sau khi thu thập đủ số lượng Viên Ngọc Thuộc Tính.</t>
+          <t>Nâng cấp Resonator sau khi thu thập đủ số lượng Viên Ngọc Thuộc Tính.</t>
         </is>
       </c>
     </row>
@@ -19944,7 +19944,7 @@
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t>Trên những vách đá cao chót vót vươn lên trời, một con rồng thực sự xuất hiện từ trong mây.</t>
+          <t>Trên những vách đá cao chót vót vươn lên trời, một con rồng đích thực hiện ra từ trong mây.</t>
         </is>
       </c>
     </row>
@@ -20009,7 +20009,7 @@
       </c>
       <c r="M301" t="inlineStr">
         <is>
-          <t>Ánh đèn mờ ảo tỏa sáng dịu dàng trên mặt hồ khi tuyết rơi nhẹ từ bầu trời.</t>
+          <t>Ánh sáng mờ ảo phủ lên mặt hồ khi tuyết rơi nhẹ từ bầu trời.</t>
         </is>
       </c>
     </row>
@@ -20074,7 +20074,7 @@
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t>Theo lời các bậc trưởng lão ở Hồng Trấn, cảnh quan kỳ bí ấy, tựa như xương rồng, có mối liên hệ sâu sắc với Jué.</t>
+          <t>Theo lời các bậc trưởng lão ở Hongzhen, cảnh quan kỳ bí ấy, tựa như xương rồng, có mối liên hệ sâu sắc với Jué.</t>
         </is>
       </c>
     </row>
@@ -20269,7 +20269,7 @@
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t>Nước trong hồ sâu dường như ngưng tụ khi một lối vào hang động mở ra.</t>
+          <t>Nước trong hồ sâu dường như ngưng tụ lại khi lối vào hố sâu mở ra.</t>
         </is>
       </c>
     </row>
@@ -20399,7 +20399,7 @@
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t>Tại rìa Núi Firmament, tiếng sóng vỗ vọng từ những tàn tích ven biển.</t>
+          <t>Bên rìa núi Firmament, tiếng vọng triều dâng từ những tàn tích ven biển.</t>
         </is>
       </c>
     </row>
@@ -20464,7 +20464,7 @@
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t>Trên những vách đá cao chót vót vươn lên trời, một con rồng thực sự xuất hiện từ trong mây.</t>
+          <t>Trên những vách đá cao chót vót vươn lên trời, một con rồng đích thực hiện ra từ trong mây.</t>
         </is>
       </c>
     </row>
@@ -20529,7 +20529,7 @@
       </c>
       <c r="M309" t="inlineStr">
         <is>
-          <t>Ánh đèn mờ ảo tỏa sáng dịu dàng trên mặt hồ khi tuyết rơi nhẹ từ bầu trời.</t>
+          <t>Ánh sáng mờ ảo phủ lên mặt hồ khi tuyết rơi nhẹ từ bầu trời.</t>
         </is>
       </c>
     </row>
@@ -20594,7 +20594,7 @@
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t>Theo lời các bậc trưởng lão ở Hồng Trấn, cảnh quan kỳ bí ấy, tựa như xương rồng, có mối liên hệ sâu sắc với Jué.</t>
+          <t>Theo lời các bậc trưởng lão ở Hongzhen, cảnh quan kỳ bí ấy, tựa như xương rồng, có mối liên hệ sâu sắc với Jué.</t>
         </is>
       </c>
     </row>
@@ -20789,7 +20789,7 @@
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t>Nước trong hồ sâu dường như ngưng tụ khi một lối vào hang động mở ra.</t>
+          <t>Nước trong hồ sâu dường như ngưng tụ lại khi lối vào hố sâu mở ra.</t>
         </is>
       </c>
     </row>
@@ -20919,7 +20919,7 @@
       </c>
       <c r="M315" t="inlineStr">
         <is>
-          <t>Tại rìa Núi Firmament, tiếng sóng vỗ vọng từ những tàn tích ven biển.</t>
+          <t>Bên rìa núi Firmament, tiếng vọng triều dâng từ những tàn tích ven biển.</t>
         </is>
       </c>
     </row>
@@ -20985,7 +20985,7 @@
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Clue]&lt;/color&gt; Nhiệm Vụ Phụ: Giữa Ngân Hà
+          <t>&lt;color=#c49e55&gt;[Manh mối]&lt;/color&gt; Nhiệm Vụ Phụ: Giữa Ngân Hà
 Nơi đây chứng kiến bước khởi đầu của dấu chân.</t>
         </is>
       </c>
@@ -21052,7 +21052,7 @@
       </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Clue]&lt;/color&gt; Nhiệm Vụ Phụ: Giữa Ngân Hà
+          <t>&lt;color=#c49e55&gt;[Manh mối]&lt;/color&gt; Nhiệm Vụ Phụ: Giữa Ngân Hà
 Nơi đây chứng kiến ý nghĩa của trách nhiệm.</t>
         </is>
       </c>
@@ -21119,7 +21119,7 @@
       </c>
       <c r="M318" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Clue]&lt;/color&gt; Nhiệm Vụ Phụ: Giữa Ngân Hà
+          <t>&lt;color=#c49e55&gt;[Manh mối]&lt;/color&gt; Nhiệm Vụ Phụ: Giữa Ngân Hà
 Nơi đây chứng kiến sự hợp lý của tính tuyệt đối.</t>
         </is>
       </c>
@@ -21186,7 +21186,7 @@
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Clue]&lt;/color&gt; Nhiệm Vụ Phụ: Giữa Bầu Trời Sao
+          <t>&lt;color=#c49e55&gt;[Manh Mối]&lt;/color&gt; Nhiệm Vụ Phụ: Giữa Bầu Trời Sao
 Nơi đây chứng kiến, ngọn đuốc của tương lai.</t>
         </is>
       </c>
@@ -21253,7 +21253,7 @@
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Clue]&lt;/color&gt; Nhiệm Vụ Phụ: Tiếng Vọng Xanh Trôi Dạt Trong Gió
+          <t>&lt;color=#c49e55&gt;[Manh Mối]&lt;/color&gt; Nhiệm Vụ Phụ: Tiếng Vọng Xanh Trôi Dạt Trong Gió
 Nơi đây chứng kiến, linh hồn tìm về dấu cũ.</t>
         </is>
       </c>
@@ -21320,7 +21320,7 @@
       </c>
       <c r="M321" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Clue]&lt;/color&gt; Nhiệm Vụ Phụ: Tiếng Vọng Xanh Trôi Dạt Trong Gió
+          <t>&lt;color=#c49e55&gt;[Manh Mối]&lt;/color&gt; Nhiệm Vụ Phụ: Tiếng Vọng Xanh Trôi Dạt Trong Gió
 Nơi đây chứng kiến, những con cá lạc loài.</t>
         </is>
       </c>
@@ -28408,7 +28408,7 @@
       </c>
       <c r="M430" t="inlineStr">
         <is>
-          <t>Giai đoạn này sẽ mở khóa trong {0}.</t>
+          <t>Giai đoạn này sẽ mở khóa vào {0}.</t>
         </is>
       </c>
     </row>
@@ -28473,7 +28473,7 @@
       </c>
       <c r="M431" t="inlineStr">
         <is>
-          <t>Triển khai ít nhất một Cộng Hưởng Giả để bắt đầu thử thách.</t>
+          <t>Triển khai ít nhất một Resonator để bắt đầu thử thách.</t>
         </is>
       </c>
     </row>
@@ -28603,7 +28603,7 @@
       </c>
       <c r="M433" t="inlineStr">
         <is>
-          <t>Suggested Lv. {0}</t>
+          <t>Cấp đề xuất: {0}</t>
         </is>
       </c>
     </row>
@@ -28668,7 +28668,7 @@
       </c>
       <c r="M434" t="inlineStr">
         <is>
-          <t>Current Points: {0}</t>
+          <t>Điểm hiện tại: {0}</t>
         </is>
       </c>
     </row>
@@ -28798,7 +28798,7 @@
       </c>
       <c r="M436" t="inlineStr">
         <is>
-          <t>Total Points đạt {0}</t>
+          <t>Tổng Điểm đạt {0}</t>
         </is>
       </c>
     </row>
@@ -29318,7 +29318,7 @@
       </c>
       <c r="M444" t="inlineStr">
         <is>
-          <t>&lt;\color=#ffd12f&gt;{0}&lt;/color&gt;/{1}</t>
+          <t>{0}/{1}</t>
         </is>
       </c>
     </row>
@@ -29515,7 +29515,7 @@
       </c>
       <c r="M447" t="inlineStr">
         <is>
-          <t>Huanglong: Ngọn núi Thiên Cung</t>
+          <t>Huanglong: Mt. Firmament</t>
         </is>
       </c>
     </row>
@@ -29840,7 +29840,7 @@
       </c>
       <c r="M452" t="inlineStr">
         <is>
-          <t>Completed: {0}/{1}</t>
+          <t>Hoàn thành: {0}/{1}</t>
         </is>
       </c>
     </row>
@@ -30360,7 +30360,7 @@
       </c>
       <c r="M460" t="inlineStr">
         <is>
-          <t>Total Points đạt {0}</t>
+          <t>Tổng Điểm đạt {0}</t>
         </is>
       </c>
     </row>
@@ -30750,7 +30750,7 @@
       </c>
       <c r="M466" t="inlineStr">
         <is>
-          <t>Cấp Độ Cộng Hưởng Giả tăng lên &lt;color=#ffd12f&gt;{0}&lt;/color&gt;</t>
+          <t>Cấp Độ Resonator tăng lên &lt;color=#ffd12f&gt;{0}&lt;/color&gt;</t>
         </is>
       </c>
     </row>
